--- a/Outputs/Scenarios/PtX_demand_BG_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BG_Electrification.xlsx
@@ -501,7 +501,7 @@
         <v>0.004129039467848634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008113821620324931</v>
+        <v>0.000811382162032493</v>
       </c>
       <c r="F2" t="n">
         <v>0.008163292693383931</v>
@@ -809,7 +809,7 @@
         <v>0.00220440146393377</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003788084439193899</v>
+        <v>0.0037880844391939</v>
       </c>
       <c r="J10" t="n">
         <v>9.263140517044296e-05</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0006762847930484333</v>
+        <v>0.0006762847930484332</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0.001347625912720067</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008992551076105413</v>
+        <v>0.008992551076105412</v>
       </c>
     </row>
     <row r="31">
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>2.525898704931292e-05</v>
+        <v>2.525898704931293e-05</v>
       </c>
       <c r="D31" t="n">
         <v>0.001304796812222275</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005995034050736943</v>
+        <v>0.005995034050736942</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.008992551076105413</v>
+        <v>0.008992551076105412</v>
       </c>
     </row>
     <row r="34">
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>1.262949352465646e-05</v>
+        <v>1.262949352465647e-05</v>
       </c>
       <c r="D42" t="n">
         <v>0.00104383744977782</v>

--- a/Outputs/Scenarios/PtX_demand_BG_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BG_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0009103253911235636</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00154435344116686</v>
+        <v>0.001913808322212921</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002573922401944767</v>
+        <v>0.0003140126653194275</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001029568960777907</v>
+        <v>0.00125605066127771</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00154435344116686</v>
+        <v>0.00125605066127771</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>7.29536466119425e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.002247815705662064</v>
+        <v>0.002206809809909508</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0004415885764233549</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02082322408772626</v>
+        <v>0.0204433553315722</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.311624796363922e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002573922401944767</v>
+        <v>0.0003140126653194275</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001347625912720067</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008992551076105412</v>
+        <v>0.01021581352220822</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001498758512684236</v>
+        <v>0.001676183970610802</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005995034050736942</v>
+        <v>0.00670473588244321</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.008992551076105412</v>
+        <v>0.00670473588244321</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>7.092767961684565e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001498758512684236</v>
+        <v>0.001676183970610802</v>
       </c>
     </row>
     <row r="43">
